--- a/kb023_insurance.xlsx
+++ b/kb023_insurance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d251688e3d9c1650/Cursor/KB023/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{ACE45949-88EB-420F-B29A-E9D07C701134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D232E3E-5DAA-4F68-BC8C-59B29A87E234}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{ACE45949-88EB-420F-B29A-E9D07C701134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22863604-B9D2-4622-B2BC-F851017EAF68}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{638095B0-49AE-4E10-A5D3-F73EE51B9C49}"/>
+    <workbookView xWindow="9165" yWindow="4335" windowWidth="21600" windowHeight="11295" xr2:uid="{638095B0-49AE-4E10-A5D3-F73EE51B9C49}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,10 +117,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>25개</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>kb-123</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -141,10 +137,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>5개</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>카드</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -157,18 +149,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>11개</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>딸1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>8개</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>딸3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -179,6 +163,20 @@
   <si>
     <t>600517-2067915</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB 더블업 역모기지 종신보험 무배당(해약환급금 미지급형)(간편심사형)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB Trust 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(해약환급금 미지급형)(납입면제형)</t>
+  </si>
+  <si>
+    <t>KB 3.10.5 딱좋은 초경증 건강보험 무배당(간편심사형)(해약환급금 미지급형)(납입면제형)</t>
   </si>
 </sst>
 </file>
@@ -435,6 +433,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -760,7 +762,7 @@
     <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="9.25" bestFit="1" customWidth="1"/>
@@ -820,28 +822,28 @@
         <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="F2" s="6">
         <v>47848</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" s="7">
         <v>10000</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J2" s="7">
         <v>500000</v>
@@ -856,21 +858,21 @@
         <v>500000</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>1</v>
@@ -879,13 +881,13 @@
         <v>47849</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" s="7">
         <v>20000</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J3" s="7">
         <v>600000</v>
@@ -900,7 +902,7 @@
         <v>600000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -908,13 +910,13 @@
         <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>2</v>
@@ -923,13 +925,13 @@
         <v>47850</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="7">
         <v>30000</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J4" s="7">
         <v>700000</v>
@@ -944,21 +946,21 @@
         <v>700000</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>4</v>
@@ -967,13 +969,13 @@
         <v>47851</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="12">
         <v>40000</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J5" s="12">
         <v>800000</v>
@@ -988,7 +990,7 @@
         <v>800000</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/kb023_insurance.xlsx
+++ b/kb023_insurance.xlsx
@@ -1,182 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d251688e3d9c1650/Cursor/KB023/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{ACE45949-88EB-420F-B29A-E9D07C701134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22863604-B9D2-4622-B2BC-F851017EAF68}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_60FDB806531FC33580592F1609A68A8B5E9DEAC1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8127723-BCC4-4E74-AA4C-8F180C48981A}"/>
   <bookViews>
-    <workbookView xWindow="9165" yWindow="4335" windowWidth="21600" windowHeight="11295" xr2:uid="{638095B0-49AE-4E10-A5D3-F73EE51B9C49}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
-  <si>
-    <t>연금보험</t>
-  </si>
-  <si>
-    <t>kb-124</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+  <si>
+    <t>계약자명</t>
+  </si>
+  <si>
+    <t>주민번호</t>
+  </si>
+  <si>
+    <t>상품종류</t>
+  </si>
+  <si>
+    <t>상품명</t>
+  </si>
+  <si>
+    <t>증권번호</t>
+  </si>
+  <si>
+    <t>납입만기</t>
+  </si>
+  <si>
+    <t>주요담보</t>
+  </si>
+  <si>
+    <t>월보험료</t>
+  </si>
+  <si>
+    <t>납입방법</t>
+  </si>
+  <si>
+    <t>납입보험료</t>
+  </si>
+  <si>
+    <t>총보험료</t>
+  </si>
+  <si>
+    <t>해지환급금</t>
+  </si>
+  <si>
+    <t>대출금</t>
+  </si>
+  <si>
+    <t>참고사항</t>
+  </si>
+  <si>
+    <t>김찬식</t>
+  </si>
+  <si>
+    <t>kb-123</t>
+  </si>
+  <si>
+    <t>아파트</t>
+  </si>
+  <si>
+    <t>이체</t>
+  </si>
+  <si>
+    <t>아버지</t>
+  </si>
+  <si>
+    <t>610623-1010432</t>
+  </si>
+  <si>
+    <t>건강/상해보험</t>
+  </si>
+  <si>
+    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(해약환급금 미지급형)(납입면제형)</t>
   </si>
   <si>
     <t>kb-125</t>
   </si>
   <si>
-    <t>변액보험</t>
-  </si>
-  <si>
-    <t>kb-126</t>
-  </si>
-  <si>
-    <t>계약자명</t>
+    <t>딸1</t>
+  </si>
+  <si>
+    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>주민번호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>보험상품</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>증권번호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>납입만기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>주요담보</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>월보험료</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>납입방법</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>납입보험료</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>총보험료</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해지환급금</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대출금</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>참고사항</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>김찬식</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>종신/정기보험</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>kb-123</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아파트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이체</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아버지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>정경희</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>카드</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>어머니</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>건강/상해보험</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>딸1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>딸3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>610623-1010432</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>600517-2067915</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB 더블업 역모기지 종신보험 무배당(해약환급금 미지급형)(간편심사형)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB Trust 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(해약환급금 미지급형)(납입면제형)</t>
-  </si>
-  <si>
-    <t>KB 3.10.5 딱좋은 초경증 건강보험 무배당(간편심사형)(해약환급금 미지급형)(납입면제형)</t>
   </si>
 </sst>
 </file>
@@ -234,7 +153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -332,46 +251,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -402,21 +291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -433,10 +308,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -755,95 +626,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C6869C-3B4B-42C4-8043-8709A3D2B29B}">
-  <dimension ref="A1:N5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="32.1" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="83.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.25" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F2" s="6">
         <v>47848</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H2" s="7">
         <v>10000</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J2" s="7">
         <v>500000</v>
@@ -858,139 +729,51 @@
         <v>500000</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F3" s="6">
-        <v>47849</v>
+        <v>47850</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H3" s="7">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J3" s="7">
-        <v>600000</v>
+        <v>700000</v>
       </c>
       <c r="K3" s="7">
         <v>1000000</v>
       </c>
       <c r="L3" s="7">
-        <v>600000</v>
+        <v>700000</v>
       </c>
       <c r="M3" s="7">
-        <v>600000</v>
+        <v>700000</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6">
-        <v>47850</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="7">
-        <v>30000</v>
-      </c>
-      <c r="I4" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="J4" s="7">
-        <v>700000</v>
-      </c>
-      <c r="K4" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="L4" s="7">
-        <v>700000</v>
-      </c>
-      <c r="M4" s="7">
-        <v>700000</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="11">
-        <v>47851</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="12">
-        <v>40000</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="12">
-        <v>800000</v>
-      </c>
-      <c r="K5" s="12">
-        <v>1000000</v>
-      </c>
-      <c r="L5" s="12">
-        <v>800000</v>
-      </c>
-      <c r="M5" s="12">
-        <v>800000</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
